--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G108"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -617,16 +617,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>founderStoryPage.heroTitle</v>
+        <v>founderStorySurfaceCopy.heroNamesLine</v>
       </c>
       <c r="B10" t="str">
-        <v>创始人故事 / 英雄区</v>
+        <v>创始人故事 / 英雄区副标题</v>
       </c>
       <c r="C10" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D10" t="str">
-        <v>Our Story Outline — 2026</v>
+        <v>John Long Woo · Caros · Sam</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -635,21 +635,21 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>founderStorySurfaceCopy — FounderStoryView chrome</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>founderStoryPage.heroBadge</v>
+        <v>founderStorySurfaceCopy.backToAbout</v>
       </c>
       <c r="B11" t="str">
-        <v>创始人故事 / 英雄区</v>
+        <v>创始人故事 / 返回</v>
       </c>
       <c r="C11" t="str">
-        <v>label</v>
+        <v>button / link</v>
       </c>
       <c r="D11" t="str">
-        <v>Founder narrative</v>
+        <v>← Organization overview</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -658,21 +658,21 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>founderStorySurfaceCopy — FounderStoryView chrome</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>founderStoryPage.intro</v>
+        <v>founderStorySurfaceCopy.legacyTimelineLink</v>
       </c>
       <c r="B12" t="str">
-        <v>创始人故事 / 引言</v>
+        <v>创始人故事 / 页脚外链</v>
       </c>
       <c r="C12" t="str">
-        <v>paragraph / other</v>
+        <v>button / link</v>
       </c>
       <c r="D12" t="str">
-        <v>I am **John Long Woo**. Together with my two sons, **Caros** and **Sam** — we three, father and sons — we have lived through too many extraordinary events involving the **spirit realm** to count. Those experiences have made us the **first door-openers to the Spirit Realm** and the **first explorers of the truth of spirit life**.</v>
+        <v>Earlier staged timeline on the legacy site</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -681,44 +681,44 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>founderStorySurfaceCopy — FounderStoryView chrome</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>founderStoryPage.truths.title</v>
+        <v>founderStorySurfaceCopy.achievementsFeaturePageLink</v>
       </c>
       <c r="B13" t="str">
-        <v>创始人故事 / 三个真相</v>
+        <v>创始人故事 / Phase B 内链（替换 {{%ACH%}}）</v>
       </c>
       <c r="C13" t="str">
-        <v>heading</v>
+        <v>button / link</v>
       </c>
       <c r="D13" t="str">
-        <v>Three truths</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>《2025直播间成就》专题页</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>founderStorySurfaceCopy — FounderStoryView chrome</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>founderStoryPage.truths.items[0].label</v>
+        <v>founderStoryPage.heroTitle</v>
       </c>
       <c r="B14" t="str">
-        <v>创始人故事 / 三个真相</v>
+        <v>创始人故事 / 英雄区</v>
       </c>
       <c r="C14" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D14" t="str">
-        <v>Truth 1</v>
+        <v>Our Story Outline — 2026</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -732,16 +732,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[0].title</v>
+        <v>founderStoryPage.heroBadge</v>
       </c>
       <c r="B15" t="str">
-        <v>创始人故事 / 三个真相</v>
+        <v>创始人故事 / 英雄区</v>
       </c>
       <c r="C15" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D15" t="str">
-        <v>Body and spirit</v>
+        <v>Founder narrative</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -755,16 +755,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[0].text</v>
+        <v>founderStoryPage.intro</v>
       </c>
       <c r="B16" t="str">
-        <v>创始人故事 / 三个真相</v>
+        <v>创始人故事 / 引言</v>
       </c>
       <c r="C16" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D16" t="str">
-        <v>A living person is composed of both the **physical body** and the **spirit (soul)**. **Spirits (ghosts)** exist after human death.</v>
+        <v>I am **John Long Woo**. Together with my two sons, **Caros** and **Sam** — we three, father and sons — we have lived through too many extraordinary events involving the **spirit realm** to count. Those experiences have made us the **first door-openers to the Spirit Realm** and the **first explorers of the truth of spirit life**.</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -778,7 +778,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[1].title</v>
+        <v>founderStoryPage.truths.title</v>
       </c>
       <c r="B17" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -787,7 +787,7 @@
         <v>heading</v>
       </c>
       <c r="D17" t="str">
-        <v>Parasitism and disease</v>
+        <v>Three truths</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -801,16 +801,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[1].text</v>
+        <v>founderStoryPage.truths.items[0].label</v>
       </c>
       <c r="B18" t="str">
         <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C18" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D18" t="str">
-        <v>For the billions of them, the only way to survive is to **attach to human beings** and draw energy. That pattern is bound up with widespread illness such as **epilepsy**, **depression**, **schizophrenia**, and **somatic symptom disorders**.</v>
+        <v>Truth 1</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -824,7 +824,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[2].title</v>
+        <v>founderStoryPage.truths.items[0].blocks[0].title</v>
       </c>
       <c r="B19" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -833,7 +833,7 @@
         <v>heading</v>
       </c>
       <c r="D19" t="str">
-        <v>Spirit Medicine</v>
+        <v>Body and spirit</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -847,7 +847,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[2].text</v>
+        <v>founderStoryPage.truths.items[0].blocks[0].text</v>
       </c>
       <c r="B20" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -856,7 +856,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D20" t="str">
-        <v>By **managing spirits (ghosts) through Master Spirits**, these conditions can often be rapidly improved. From that work we created **Spirit Medicine**.</v>
+        <v>A living person is composed of both the **physical body** and the **spirit (soul)**. **Spirits (ghosts)** exist after human death.</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -870,7 +870,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[3].title</v>
+        <v>founderStoryPage.truths.items[0].blocks[1].title</v>
       </c>
       <c r="B21" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -879,7 +879,7 @@
         <v>heading</v>
       </c>
       <c r="D21" t="str">
-        <v>Archives</v>
+        <v>Parasitism and disease</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -893,7 +893,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>founderStoryPage.truths.items[0].blocks[3].text</v>
+        <v>founderStoryPage.truths.items[0].blocks[1].text</v>
       </c>
       <c r="B22" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -902,7 +902,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D22" t="str">
-        <v>Further documentation appears in **Woos Record of Soul** and the **Woos Spirit Medicine** video archives.</v>
+        <v>For the billions of them, the only way to survive is to **attach to human beings** and draw energy. That pattern is bound up with widespread illness such as **epilepsy**, **depression**, **schizophrenia**, and **somatic symptom disorders**.</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -916,16 +916,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>founderStoryPage.truths.items[1].label</v>
+        <v>founderStoryPage.truths.items[0].blocks[2].title</v>
       </c>
       <c r="B23" t="str">
         <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C23" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D23" t="str">
-        <v>Truth 2</v>
+        <v>Spirit Medicine</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -939,7 +939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>founderStoryPage.truths.items[1].blocks[0].text</v>
+        <v>founderStoryPage.truths.items[0].blocks[2].text</v>
       </c>
       <c r="B24" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -948,7 +948,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D24" t="str">
-        <v>The **Spirit Realm** has governors — tremendous **Master Spirits**, upgraded from ordinary spirits through the **Universal Matrix of Meta Awareness**.</v>
+        <v>By **managing spirits (ghosts) through Master Spirits**, these conditions can often be rapidly improved. From that work we created **Spirit Medicine**.</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -962,16 +962,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>founderStoryPage.truths.items[2].label</v>
+        <v>founderStoryPage.truths.items[0].blocks[3].title</v>
       </c>
       <c r="B25" t="str">
         <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C25" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D25" t="str">
-        <v>Truth 3</v>
+        <v>Archives</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -985,7 +985,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>founderStoryPage.truths.items[2].blocks[0].text</v>
+        <v>founderStoryPage.truths.items[0].blocks[3].text</v>
       </c>
       <c r="B26" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -994,7 +994,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D26" t="str">
-        <v>The **Universal Matrix of Meta Awareness** is the **true creator-level substrate**; **our universe is part of its body**.</v>
+        <v>Further documentation appears in **Woos Record of Soul** and the **Woos Spirit Medicine** video archives.</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1008,16 +1008,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>founderStoryPage.truths.items[2].blocks[1].title</v>
+        <v>founderStoryPage.truths.items[1].label</v>
       </c>
       <c r="B27" t="str">
         <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C27" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D27" t="str">
-        <v>Archive</v>
+        <v>Truth 2</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>founderStoryPage.truths.items[2].blocks[1].text</v>
+        <v>founderStoryPage.truths.items[1].blocks[0].text</v>
       </c>
       <c r="B28" t="str">
         <v>创始人故事 / 三个真相</v>
@@ -1040,7 +1040,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D28" t="str">
-        <v>Further documentation appears in the **Universal Matrix of Meta Awareness** video archive.</v>
+        <v>The **Spirit Realm** has governors — tremendous **Master Spirits**, upgraded from ordinary spirits through the **Universal Matrix of Meta Awareness**.</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>founderStoryPage.phasesOverview.title</v>
+        <v>founderStoryPage.truths.items[2].label</v>
       </c>
       <c r="B29" t="str">
-        <v>创始人故事 / 两大阶段</v>
+        <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C29" t="str">
-        <v>heading</v>
+        <v>label</v>
       </c>
       <c r="D29" t="str">
-        <v>Two major chapters</v>
+        <v>Truth 3</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1077,16 +1077,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>founderStoryPage.phasesOverview.a.title</v>
+        <v>founderStoryPage.truths.items[2].blocks[0].text</v>
       </c>
       <c r="B30" t="str">
-        <v>创始人故事 / Phase A 概要</v>
+        <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C30" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D30" t="str">
-        <v>Phase A — May 2014 through February 2025</v>
+        <v>The **Universal Matrix of Meta Awareness** is the **true creator-level substrate**; **our universe is part of its body**.</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1100,16 +1100,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[0].title</v>
+        <v>founderStoryPage.truths.items[2].blocks[1].title</v>
       </c>
       <c r="B31" t="str">
-        <v>创始人故事 / Phase A 概要</v>
+        <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C31" t="str">
         <v>heading</v>
       </c>
       <c r="D31" t="str">
-        <v>Who was involved</v>
+        <v>Archive</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1123,16 +1123,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[0].text</v>
+        <v>founderStoryPage.truths.items[2].blocks[1].text</v>
       </c>
       <c r="B32" t="str">
-        <v>创始人故事 / Phase A 概要</v>
+        <v>创始人故事 / 三个真相</v>
       </c>
       <c r="C32" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D32" t="str">
-        <v>We fought **attached spirits** of different classes parasitizing our bodies — including a **Class-C1**-level entity (archive designation associated with the “**Hui’an**” tier), the **Class-C2** spirit **Qing Xiaoxian**, and the **Class-C3** spirit **Qian Kai**. They drove **severe illness across our family**.</v>
+        <v>Further documentation appears in the **Universal Matrix of Meta Awareness** video archive.</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1146,16 +1146,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[1].title</v>
+        <v>founderStoryPage.phasesOverview.title</v>
       </c>
       <c r="B33" t="str">
-        <v>创始人故事 / Phase A 概要</v>
+        <v>创始人故事 / 两大阶段</v>
       </c>
       <c r="C33" t="str">
         <v>heading</v>
       </c>
       <c r="D33" t="str">
-        <v>Motive and methods</v>
+        <v>Two major chapters</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1169,16 +1169,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[1].text</v>
+        <v>founderStoryPage.phasesOverview.a.title</v>
       </c>
       <c r="B34" t="str">
         <v>创始人故事 / Phase A 概要</v>
       </c>
       <c r="C34" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D34" t="str">
-        <v>Our only motive was **self-rescue**: we tried every means we could to harm or destroy them. In doing so we learned the **physiological and physical properties of ghost bodies**, and communicated through **epileptic discharge**, **auditory hallucination sounds**, **consciousness dialogue**, **consciousness control**, and related modes — building a large, verified picture of the spirit world.</v>
+        <v>Phase A — May 2014 through February 2025</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[2].title</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[0].title</v>
       </c>
       <c r="B35" t="str">
         <v>创始人故事 / Phase A 概要</v>
@@ -1201,7 +1201,7 @@
         <v>heading</v>
       </c>
       <c r="D35" t="str">
-        <v>Regret</v>
+        <v>Who was involved</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[2].text</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[0].text</v>
       </c>
       <c r="B36" t="str">
         <v>创始人故事 / Phase A 概要</v>
@@ -1224,7 +1224,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D36" t="str">
-        <v>Our greatest regret in **Phase A** is that we did **not** systematically engage attached spirits on **other human hosts** outside our family, or in **other countries**.</v>
+        <v>We fought **attached spirits** of different classes parasitizing our bodies — including a **Class-C1**-level entity (archive designation associated with the “**Hui’an**” tier), the **Class-C2** spirit **Qing Xiaoxian**, and the **Class-C3** spirit **Qian Kai**. They drove **severe illness across our family**.</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[3].title</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[1].title</v>
       </c>
       <c r="B37" t="str">
         <v>创始人故事 / Phase A 概要</v>
@@ -1247,7 +1247,7 @@
         <v>heading</v>
       </c>
       <c r="D37" t="str">
-        <v>Record</v>
+        <v>Motive and methods</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>founderStoryPage.phasesOverview.a.blocks[3].text</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[1].text</v>
       </c>
       <c r="B38" t="str">
         <v>创始人故事 / Phase A 概要</v>
@@ -1270,7 +1270,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D38" t="str">
-        <v>During this period we filmed **Woos Record of Soul**.</v>
+        <v>Our only motive was **self-rescue**: we tried every means we could to harm or destroy them. In doing so we learned the **physiological and physical properties of ghost bodies**, and communicated through **epileptic discharge**, **auditory hallucination sounds**, **consciousness dialogue**, **consciousness control**, and related modes — building a large, verified picture of the spirit world.</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1284,16 +1284,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>founderStoryPage.phaseAStages[0].label</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[2].title</v>
       </c>
       <c r="B39" t="str">
-        <v>创始人故事 / A 阶段</v>
+        <v>创始人故事 / Phase A 概要</v>
       </c>
       <c r="C39" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D39" t="str">
-        <v>A 1</v>
+        <v>Regret</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>founderStoryPage.phaseAStages[0].stageTitle</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[2].text</v>
       </c>
       <c r="B40" t="str">
-        <v>创始人故事 / A 阶段</v>
+        <v>创始人故事 / Phase A 概要</v>
       </c>
       <c r="C40" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D40" t="str">
-        <v>Stage 1 · Cheating Period 1</v>
+        <v>Our greatest regret in **Phase A** is that we did **not** systematically engage attached spirits on **other human hosts** outside our family, or in **other countries**.</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1330,16 +1330,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>founderStoryPage.phaseAStages[0].range</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[3].title</v>
       </c>
       <c r="B41" t="str">
-        <v>创始人故事 / A 阶段</v>
+        <v>创始人故事 / Phase A 概要</v>
       </c>
       <c r="C41" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D41" t="str">
-        <v>March 2018 — July 2020</v>
+        <v>Record</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1353,16 +1353,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>founderStoryPage.phaseAStages[0].paragraphs[0]</v>
+        <v>founderStoryPage.phasesOverview.a.blocks[3].text</v>
       </c>
       <c r="B42" t="str">
-        <v>创始人故事 / A 阶段</v>
+        <v>创始人故事 / Phase A 概要</v>
       </c>
       <c r="C42" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D42" t="str">
-        <v>During this period, the **low-level soul** in my body used **high-voltage electrostatic discharge** into drinks and wine to change their taste, aiming to fabricate a chain of “scientific” phenomena and laws that would ultimately “prove” **Buddhism**.</v>
+        <v>During this period we filmed **Woos Record of Soul**.</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1376,16 +1376,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>founderStoryPage.phaseAStages[0].paragraphs[1]</v>
+        <v>founderStoryPage.phaseAStages[0].label</v>
       </c>
       <c r="B43" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C43" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D43" t="str">
-        <v>The details are too intricate to spell out fully in words.</v>
+        <v>A 1</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1399,16 +1399,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>founderStoryPage.phaseAStages[0].storylineClip.figureAlt</v>
+        <v>founderStoryPage.phaseAStages[0].stageTitle</v>
       </c>
       <c r="B44" t="str">
-        <v>创始人故事 / A 阶段 / 配图</v>
+        <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C44" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D44" t="str">
-        <v>Wine and glassware in candlelight — visual echo of the “altered drink” period described in Stage 1</v>
+        <v>Stage 1 · Cheating Period 1</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>founderStoryPage.phaseAStages[1].label</v>
+        <v>founderStoryPage.phaseAStages[0].range</v>
       </c>
       <c r="B45" t="str">
         <v>创始人故事 / A 阶段</v>
@@ -1431,7 +1431,7 @@
         <v>label</v>
       </c>
       <c r="D45" t="str">
-        <v>A 2</v>
+        <v>March 2018 — July 2020</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1445,16 +1445,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>founderStoryPage.phaseAStages[1].stageTitle</v>
+        <v>founderStoryPage.phaseAStages[0].paragraphs[0]</v>
       </c>
       <c r="B46" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C46" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D46" t="str">
-        <v>Cheating period 2</v>
+        <v>During this period, the **low-level soul** in my body used **high-voltage electrostatic discharge** into drinks and wine to change their taste, aiming to fabricate a chain of “scientific” phenomena and laws that would ultimately “prove” **Buddhism**.</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1468,16 +1468,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>founderStoryPage.phaseAStages[1].range</v>
+        <v>founderStoryPage.phaseAStages[0].paragraphs[1]</v>
       </c>
       <c r="B47" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C47" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D47" t="str">
-        <v>July 2020 — 15 November 2020</v>
+        <v>The details are too intricate to spell out fully in words.</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -1491,16 +1491,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>founderStoryPage.phaseAStages[1].paragraphs[0]</v>
+        <v>founderStoryPage.phaseAStages[0].storylineClip.figureAlt</v>
       </c>
       <c r="B48" t="str">
-        <v>创始人故事 / A 阶段</v>
+        <v>创始人故事 / A 阶段 / 配图</v>
       </c>
       <c r="C48" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D48" t="str">
-        <v>During this interval, the low-level soul used **epilepsy-like seizures** to impersonate, in sequence, the **three greatest gods of Buddhism**, pretending to convey **divine will** — until my sons and I had converted.</v>
+        <v>Wine and glassware in candlelight — visual echo of the “altered drink” period described in Stage 1</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>founderStoryPage.phaseAStages[1].paragraphs[1]</v>
+        <v>founderStoryPage.phaseAStages[1].label</v>
       </c>
       <c r="B49" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C49" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D49" t="str">
-        <v>It was a **grotesque joke**; we were **playthings**. Even so, we exchanged a great deal of **philosophical insight** during the deception.</v>
+        <v>A 2</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -1537,16 +1537,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>founderStoryPage.phaseAStages[1].storylineClip.figureAlt</v>
+        <v>founderStoryPage.phaseAStages[1].stageTitle</v>
       </c>
       <c r="B50" t="str">
-        <v>创始人故事 / A 阶段 / 配图</v>
+        <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C50" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D50" t="str">
-        <v>Golden Buddha statue — atmosphere of the religious theatre described in Stage 2</v>
+        <v>Cheating period 2</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>founderStoryPage.phaseAStages[2].label</v>
+        <v>founderStoryPage.phaseAStages[1].range</v>
       </c>
       <c r="B51" t="str">
         <v>创始人故事 / A 阶段</v>
@@ -1569,7 +1569,7 @@
         <v>label</v>
       </c>
       <c r="D51" t="str">
-        <v>A 3</v>
+        <v>July 2020 — 15 November 2020</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -1583,16 +1583,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>founderStoryPage.phaseAStages[2].stageTitle</v>
+        <v>founderStoryPage.phaseAStages[1].paragraphs[0]</v>
       </c>
       <c r="B52" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C52" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D52" t="str">
-        <v>Exorcism period 1</v>
+        <v>During this interval, the low-level soul used **epilepsy-like seizures** to impersonate, in sequence, the **three greatest gods of Buddhism**, pretending to convey **divine will** — until my sons and I had converted.</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -1606,16 +1606,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>founderStoryPage.phaseAStages[2].range</v>
+        <v>founderStoryPage.phaseAStages[1].paragraphs[1]</v>
       </c>
       <c r="B53" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C53" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D53" t="str">
-        <v>15 November 2020 — July 2021</v>
+        <v>It was a **grotesque joke**; we were **playthings**. Even so, we exchanged a great deal of **philosophical insight** during the deception.</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -1629,16 +1629,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>founderStoryPage.phaseAStages[2].paragraphs[0]</v>
+        <v>founderStoryPage.phaseAStages[1].storylineClip.figureAlt</v>
       </c>
       <c r="B54" t="str">
-        <v>创始人故事 / A 阶段</v>
+        <v>创始人故事 / A 阶段 / 配图</v>
       </c>
       <c r="C54" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D54" t="str">
-        <v>On **15 November 2020**, the **true identities** of the souls inside us and their **tricks** were finally exposed. In fear and rage we tried to **exorcise** them.</v>
+        <v>Golden Buddha statue — atmosphere of the religious theatre described in Stage 2</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -1652,16 +1652,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>founderStoryPage.phaseAStages[2].paragraphs[1]</v>
+        <v>founderStoryPage.phaseAStages[2].label</v>
       </c>
       <c r="B55" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C55" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D55" t="str">
-        <v>Traditional methods failed repeatedly; we remembered they had always **forbidden** us to touch **strong magnets**. We began using magnets to **hurt** them.</v>
+        <v>A 3</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -1675,16 +1675,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>founderStoryPage.phaseAStages[2].paragraphs[2]</v>
+        <v>founderStoryPage.phaseAStages[2].stageTitle</v>
       </c>
       <c r="B56" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C56" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D56" t="str">
-        <v>Within days the soul in my **elder son** could not endure it and **left first**; about **six weeks** later the soul in my **younger son** left for the same reason.</v>
+        <v>Exorcism period 1</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -1698,16 +1698,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>founderStoryPage.phaseAStages[2].paragraphs[3]</v>
+        <v>founderStoryPage.phaseAStages[2].range</v>
       </c>
       <c r="B57" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C57" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D57" t="str">
-        <v>The soul in **me** refused to depart even when injured. I found that a **strong electrostatic field** could severely weaken its discharging: my **epilepsy vanished** the moment that happened — yet the soul **remained inside**, playing hide-and-seek.</v>
+        <v>15 November 2020 — July 2021</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -1721,16 +1721,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>founderStoryPage.phaseAStages[3].label</v>
+        <v>founderStoryPage.phaseAStages[2].paragraphs[0]</v>
       </c>
       <c r="B58" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C58" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D58" t="str">
-        <v>A 4</v>
+        <v>On **15 November 2020**, the **true identities** of the souls inside us and their **tricks** were finally exposed. In fear and rage we tried to **exorcise** them.</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -1744,16 +1744,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>founderStoryPage.phaseAStages[3].stageTitle</v>
+        <v>founderStoryPage.phaseAStages[2].paragraphs[1]</v>
       </c>
       <c r="B59" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C59" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D59" t="str">
-        <v>Exorcism period 2 · and high-level revealing</v>
+        <v>Traditional methods failed repeatedly; we remembered they had always **forbidden** us to touch **strong magnets**. We began using magnets to **hurt** them.</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -1767,16 +1767,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>founderStoryPage.phaseAStages[3].range</v>
+        <v>founderStoryPage.phaseAStages[2].paragraphs[2]</v>
       </c>
       <c r="B60" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C60" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D60" t="str">
-        <v>July 2021 — 4 April 2022</v>
+        <v>Within days the soul in my **elder son** could not endure it and **left first**; about **six weeks** later the soul in my **younger son** left for the same reason.</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>founderStoryPage.phaseAStages[3].paragraphs[0]</v>
+        <v>founderStoryPage.phaseAStages[2].paragraphs[3]</v>
       </c>
       <c r="B61" t="str">
         <v>创始人故事 / A 阶段</v>
@@ -1799,7 +1799,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D61" t="str">
-        <v>In this stage we **found and confirmed** several ways to interfere with, injure, and **kill ordinary souls**.</v>
+        <v>The soul in **me** refused to depart even when injured. I found that a **strong electrostatic field** could severely weaken its discharging: my **epilepsy vanished** the moment that happened — yet the soul **remained inside**, playing hide-and-seek.</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -1813,16 +1813,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>founderStoryPage.phaseAStages[3].paragraphs[1]</v>
+        <v>founderStoryPage.phaseAStages[3].label</v>
       </c>
       <c r="B62" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C62" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D62" t="str">
-        <v>The limits of **electrostatic and magnet** work drew the attention of a **high-level soul** who had died in China roughly **1,500 years ago**. It joined the exploration: **consciousness transmission** for hints, while **steering the ordinary soul’s behavior** until I learned how to kill and expel **precisely and efficiently**.</v>
+        <v>A 4</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -1836,16 +1836,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>founderStoryPage.phaseAStages[3].paragraphs[2]</v>
+        <v>founderStoryPage.phaseAStages[3].stageTitle</v>
       </c>
       <c r="B63" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C63" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D63" t="str">
-        <v>Each day I **tangled, fought, and coexisted** with the ordinary soul — **enemy and ally** at once — and traded large amounts of **spirit-relevant knowledge**.</v>
+        <v>Exorcism period 2 · and high-level revealing</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -1859,16 +1859,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>founderStoryPage.phaseAStages[3].paragraphs[3]</v>
+        <v>founderStoryPage.phaseAStages[3].range</v>
       </c>
       <c r="B64" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C64" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D64" t="str">
-        <v>Finally the high-level soul **disclosed itself**, demonstrated **extraordinary abilities**, cleared up a year of confusion, taught me more of the **soul world** — then **left my body** and vanished quickly.</v>
+        <v>July 2021 — 4 April 2022</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -1882,16 +1882,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>founderStoryPage.phaseAStages[4].label</v>
+        <v>founderStoryPage.phaseAStages[3].paragraphs[0]</v>
       </c>
       <c r="B65" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C65" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D65" t="str">
-        <v>A 5</v>
+        <v>In this stage we **found and confirmed** several ways to interfere with, injure, and **kill ordinary souls**.</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -1905,16 +1905,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>founderStoryPage.phaseAStages[4].stageTitle</v>
+        <v>founderStoryPage.phaseAStages[3].paragraphs[1]</v>
       </c>
       <c r="B66" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C66" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D66" t="str">
-        <v>Class-C2 Qing Xiaoxian · Class-C3 Qian Kai</v>
+        <v>The limits of **electrostatic and magnet** work drew the attention of a **high-level soul** who had died in China roughly **1,500 years ago**. It joined the exploration: **consciousness transmission** for hints, while **steering the ordinary soul’s behavior** until I learned how to kill and expel **precisely and efficiently**.</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -1928,16 +1928,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>founderStoryPage.phaseAStages[4].range</v>
+        <v>founderStoryPage.phaseAStages[3].paragraphs[2]</v>
       </c>
       <c r="B67" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C67" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D67" t="str">
-        <v>December 2023 — January 2025</v>
+        <v>Each day I **tangled, fought, and coexisted** with the ordinary soul — **enemy and ally** at once — and traded large amounts of **spirit-relevant knowledge**.</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>founderStoryPage.phaseAStages[4].paragraphs[0]</v>
+        <v>founderStoryPage.phaseAStages[3].paragraphs[3]</v>
       </c>
       <c r="B68" t="str">
         <v>创始人故事 / A 阶段</v>
@@ -1960,7 +1960,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D68" t="str">
-        <v>In **December 2023** I was again possessed by the **Class-C2** spirit **Qing Xiaoxian**. Across roughly **1,700 years** as a ghost it had devoured on the order of **5,000–10,000** other souls, becoming an **enormous entity**.</v>
+        <v>Finally the high-level soul **disclosed itself**, demonstrated **extraordinary abilities**, cleared up a year of confusion, taught me more of the **soul world** — then **left my body** and vanished quickly.</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>founderStoryPage.phaseAStages[4].paragraphs[1]</v>
+        <v>founderStoryPage.phaseAStages[4].label</v>
       </c>
       <c r="B69" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C69" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D69" t="str">
-        <v>It turned the Woo home into a **haunted-house field**, spun **multiple avatars** onto both sons, and allowed its **core form** to coordinate those fragments **remotely**.</v>
+        <v>A 5</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -1997,16 +1997,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>founderStoryPage.phaseAStages[4].paragraphs[2]</v>
+        <v>founderStoryPage.phaseAStages[4].stageTitle</v>
       </c>
       <c r="B70" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C70" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D70" t="str">
-        <v>In the father: **schizophrenia**, **bipolar disorder**, **epilepsy**, **somatization**, and **powerful electrical assaults** on the heart. In the sons: **fatigue (energy coupling)**, **depression**, **pain disorder**, **IBS**, and further somatic patterns.</v>
+        <v>Class-C2 Qing Xiaoxian · Class-C3 Qian Kai</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -2020,16 +2020,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>founderStoryPage.phaseAStages[4].paragraphs[3]</v>
+        <v>founderStoryPage.phaseAStages[4].range</v>
       </c>
       <c r="B71" t="str">
         <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C71" t="str">
-        <v>paragraph / other</v>
+        <v>label</v>
       </c>
       <c r="D71" t="str">
-        <v>Father and sons continued to refine **exorcism** and **ghost-neutralization** until this entity was **fully destroyed**.</v>
+        <v>December 2023 — January 2025</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>founderStoryPage.phaseAStages[4].paragraphs[4]</v>
+        <v>founderStoryPage.phaseAStages[4].paragraphs[0]</v>
       </c>
       <c r="B72" t="str">
         <v>创始人故事 / A 阶段</v>
@@ -2052,7 +2052,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D72" t="str">
-        <v>From **September 2024** through **January 2025** I was possessed again by the **Class-C3** spirit **Qian Kai**. **Higher ghost density means greater power** — so Qian Kai **exceeded** Qing Xiaoxian in **thought-control** and **pathogenic force**. We continued **self-rescue** until this spirit, too, was **eliminated**.</v>
+        <v>In **December 2023** I was again possessed by the **Class-C2** spirit **Qing Xiaoxian**. Across roughly **1,700 years** as a ghost it had devoured on the order of **5,000–10,000** other souls, becoming an **enormous entity**.</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -2066,16 +2066,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>founderStoryPage.phaseB.title</v>
+        <v>founderStoryPage.phaseAStages[4].paragraphs[1]</v>
       </c>
       <c r="B73" t="str">
-        <v>创始人故事 / Phase B</v>
+        <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C73" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D73" t="str">
-        <v>B阶段：2025年2月至2026年3月</v>
+        <v>It turned the Woo home into a **haunted-house field**, spun **multiple avatars** onto both sons, and allowed its **core form** to coordinate those fragments **remotely**.</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -2089,16 +2089,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>founderStoryPage.phaseB.blocks[0].title</v>
+        <v>founderStoryPage.phaseAStages[4].paragraphs[2]</v>
       </c>
       <c r="B74" t="str">
-        <v>创始人故事 / Phase B</v>
+        <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C74" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D74" t="str">
-        <v>直播间规模与成就记录</v>
+        <v>In the father: **schizophrenia**, **bipolar disorder**, **epilepsy**, **somatization**, and **powerful electrical assaults** on the heart. In the sons: **fatigue (energy coupling)**, **depression**, **pain disorder**, **IBS**, and further somatic patterns.</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -2112,16 +2112,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>founderStoryPage.phaseB.blocks[0].text</v>
+        <v>founderStoryPage.phaseAStages[4].paragraphs[3]</v>
       </c>
       <c r="B75" t="str">
-        <v>创始人故事 / Phase B</v>
+        <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C75" t="str">
         <v>paragraph / other</v>
       </c>
       <c r="D75" t="str">
-        <v>从 **2025年2月19日** 至 **12月24日**，**Caros** 在 **TikTok** 上总共进行了 **265 场直播**；在直播间取得了 **超凡的成就**。完整记录与链接见：{{%ACH%}}</v>
+        <v>Father and sons continued to refine **exorcism** and **ghost-neutralization** until this entity was **fully destroyed**.</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -2135,16 +2135,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>founderStoryPage.phaseB.blocks[1].title</v>
+        <v>founderStoryPage.phaseAStages[4].paragraphs[4]</v>
       </c>
       <c r="B76" t="str">
-        <v>创始人故事 / Phase B</v>
+        <v>创始人故事 / A 阶段</v>
       </c>
       <c r="C76" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D76" t="str">
-        <v>Master Spirit、混合灵与远程能力</v>
+        <v>From **September 2024** through **January 2025** I was possessed again by the **Class-C3** spirit **Qian Kai**. **Higher ghost density means greater power** — so Qian Kai **exceeded** Qing Xiaoxian in **thought-control** and **pathogenic force**. We continued **self-rescue** until this spirit, too, was **eliminated**.</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -2158,19 +2158,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>founderStoryPage.phaseB.blocks[1].text</v>
+        <v>founderStoryPage.phaseB.title</v>
       </c>
       <c r="B77" t="str">
         <v>创始人故事 / Phase B</v>
       </c>
       <c r="C77" t="str">
-        <v>paragraph / other</v>
+        <v>heading</v>
       </c>
       <c r="D77" t="str">
-        <v>大量的 **Master Spirit** 以及 **混合灵（hybrid spirit）** 与我们父子联系，让我们知道灵魂世界竟然有 **管理者** 与 **造物主** 层面的秩序。**Master Spirit** 给我们很多帮助与 **特别的超常力量**，使 **Caros** 在中国就可以 **远程制约** 远在地球另一端北美附体的鬼魂。</v>
+        <v/>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>B阶段：2025年2月至2026年3月</v>
       </c>
       <c r="F77" t="str">
         <v/>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>founderStoryPage.phaseB.blocks[2].title</v>
+        <v>founderStoryPage.phaseB.blocks[0].title</v>
       </c>
       <c r="B78" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2190,10 +2190,10 @@
         <v>heading</v>
       </c>
       <c r="D78" t="str">
-        <v>关于 A 阶段附体安排的说明</v>
+        <v/>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>直播间规模与成就记录</v>
       </c>
       <c r="F78" t="str">
         <v/>
@@ -2204,7 +2204,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>founderStoryPage.phaseB.blocks[2].text</v>
+        <v>founderStoryPage.phaseB.blocks[0].text</v>
       </c>
       <c r="B79" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2213,10 +2213,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D79" t="str">
-        <v>**最重要的是**，我们被告知：**A 阶段** 在我们身上附体的鬼魂都是被 **Master Spirit** **刻意安排** 进来的；这些附体之灵被清除是 **被许可作为研究使用** 的。</v>
+        <v/>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>从 **2025年2月19日** 至 **12月24日**，**Caros** 在 **TikTok** 上总共进行了 **265 场直播**；在直播间取得了 **超凡的成就**。完整记录与链接见：{{%ACH%}}</v>
       </c>
       <c r="F79" t="str">
         <v/>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>founderStoryPage.phaseB.blocks[3].title</v>
+        <v>founderStoryPage.phaseB.blocks[1].title</v>
       </c>
       <c r="B80" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2236,10 +2236,10 @@
         <v>heading</v>
       </c>
       <c r="D80" t="str">
-        <v>计划中的病痛与叙事</v>
+        <v/>
       </c>
       <c r="E80" t="str">
-        <v/>
+        <v>Master Spirit、混合灵与远程能力</v>
       </c>
       <c r="F80" t="str">
         <v/>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>founderStoryPage.phaseB.blocks[3].text</v>
+        <v>founderStoryPage.phaseB.blocks[1].text</v>
       </c>
       <c r="B81" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2259,10 +2259,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D81" t="str">
-        <v>所有的 **病痛折磨**、**欺骗**、**戏弄性的故事** 也是他们计划的一部分，让我们了解其 **行事风格** 与 **性格秉性**。</v>
+        <v/>
       </c>
       <c r="E81" t="str">
-        <v/>
+        <v>大量的 **Master Spirit** 以及 **混合灵（hybrid spirit）** 与我们父子联系，让我们知道灵魂世界竟然有 **管理者** 与 **造物主** 层面的秩序。**Master Spirit** 给我们很多帮助与 **特别的超常力量**，使 **Caros** 在中国就可以 **远程制约** 远在地球另一端北美附体的鬼魂。</v>
       </c>
       <c r="F81" t="str">
         <v/>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>founderStoryPage.phaseB.blocks[4].title</v>
+        <v>founderStoryPage.phaseB.blocks[2].title</v>
       </c>
       <c r="B82" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2282,10 +2282,10 @@
         <v>heading</v>
       </c>
       <c r="D82" t="str">
-        <v>对 Master Spirit 品性的认识</v>
+        <v/>
       </c>
       <c r="E82" t="str">
-        <v/>
+        <v>关于 A 阶段附体安排的说明</v>
       </c>
       <c r="F82" t="str">
         <v/>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>founderStoryPage.phaseB.blocks[4].text</v>
+        <v>founderStoryPage.phaseB.blocks[2].text</v>
       </c>
       <c r="B83" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2305,10 +2305,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D83" t="str">
-        <v>这也让我们完整认识到：**Master Spirit** 并非像我们想象中的 **天使般的善良**；先前提供的帮助 **并非出于善良**，而是 **万有元神母体** 给他们安排的工作。大家可以通过 **A 阶段故事** 充分体会 **Master Spirit 团队的性格属性**。</v>
+        <v/>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>**最重要的是**，我们被告知：**A 阶段** 在我们身上附体的鬼魂都是被 **Master Spirit** **刻意安排** 进来的；这些附体之灵被清除是 **被许可作为研究使用** 的。</v>
       </c>
       <c r="F83" t="str">
         <v/>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>founderStoryPage.phaseB.blocks[5].title</v>
+        <v>founderStoryPage.phaseB.blocks[3].title</v>
       </c>
       <c r="B84" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2328,10 +2328,10 @@
         <v>heading</v>
       </c>
       <c r="D84" t="str">
-        <v>灵魂医学与影像档案</v>
+        <v/>
       </c>
       <c r="E84" t="str">
-        <v/>
+        <v>计划中的病痛与叙事</v>
       </c>
       <c r="F84" t="str">
         <v/>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>founderStoryPage.phaseB.blocks[5].text</v>
+        <v>founderStoryPage.phaseB.blocks[3].text</v>
       </c>
       <c r="B85" t="str">
         <v>创始人故事 / Phase B</v>
@@ -2351,10 +2351,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D85" t="str">
-        <v>在此期间，**正式创建了灵魂医学**；拍摄了 **《吴氏灵魂医学》** 与 **《万有元神母体》** 系列视频档案中的 **一部分视频**。</v>
+        <v/>
       </c>
       <c r="E85" t="str">
-        <v/>
+        <v>所有的 **病痛折磨**、**欺骗**、**戏弄性的故事** 也是他们计划的一部分，让我们了解其 **行事风格** 与 **性格秉性**。</v>
       </c>
       <c r="F85" t="str">
         <v/>
@@ -2365,19 +2365,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>founderTimeline[0].range</v>
+        <v>founderStoryPage.phaseB.blocks[4].title</v>
       </c>
       <c r="B86" t="str">
-        <v>创始人故事 / 年表</v>
+        <v>创始人故事 / Phase B</v>
       </c>
       <c r="C86" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D86" t="str">
-        <v>May 2014 — Feb 2025</v>
+        <v/>
       </c>
       <c r="E86" t="str">
-        <v/>
+        <v>对 Master Spirit 品性的认识</v>
       </c>
       <c r="F86" t="str">
         <v/>
@@ -2388,19 +2388,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>founderTimeline[0].label</v>
+        <v>founderStoryPage.phaseB.blocks[4].text</v>
       </c>
       <c r="B87" t="str">
-        <v>创始人故事 / 年表</v>
+        <v>创始人故事 / Phase B</v>
       </c>
       <c r="C87" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D87" t="str">
-        <v>Phase A — family field work</v>
+        <v/>
       </c>
       <c r="E87" t="str">
-        <v/>
+        <v>这也让我们完整认识到：**Master Spirit** 并非像我们想象中的 **天使般的善良**；先前提供的帮助 **并非出于善良**，而是 **万有元神母体** 给他们安排的工作。大家可以通过 **A 阶段故事** 充分体会 **Master Spirit 团队的性格属性**。</v>
       </c>
       <c r="F87" t="str">
         <v/>
@@ -2411,19 +2411,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>founderTimeline[1].range</v>
+        <v>founderStoryPage.phaseB.blocks[5].title</v>
       </c>
       <c r="B88" t="str">
-        <v>创始人故事 / 年表</v>
+        <v>创始人故事 / Phase B</v>
       </c>
       <c r="C88" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D88" t="str">
-        <v>Mar 2018 — Jul 2020</v>
+        <v/>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>灵魂医学与影像档案</v>
       </c>
       <c r="F88" t="str">
         <v/>
@@ -2434,19 +2434,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>founderTimeline[1].label</v>
+        <v>founderStoryPage.phaseB.blocks[5].text</v>
       </c>
       <c r="B89" t="str">
-        <v>创始人故事 / 年表</v>
+        <v>创始人故事 / Phase B</v>
       </c>
       <c r="C89" t="str">
-        <v>label</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D89" t="str">
-        <v>Cheating Period 1</v>
+        <v/>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>在此期间，**正式创建了灵魂医学**；拍摄了 **《吴氏灵魂医学》** 与 **《万有元神母体》** 系列视频档案中的 **一部分视频**。</v>
       </c>
       <c r="F89" t="str">
         <v/>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>founderTimeline[2].range</v>
+        <v>founderTimeline[0].range</v>
       </c>
       <c r="B90" t="str">
         <v>创始人故事 / 年表</v>
@@ -2466,7 +2466,7 @@
         <v>label</v>
       </c>
       <c r="D90" t="str">
-        <v>Jul 2020 — Nov 2020</v>
+        <v>May 2014 — Feb 2025</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>founderTimeline[2].label</v>
+        <v>founderTimeline[0].label</v>
       </c>
       <c r="B91" t="str">
         <v>创始人故事 / 年表</v>
@@ -2489,7 +2489,7 @@
         <v>label</v>
       </c>
       <c r="D91" t="str">
-        <v>Cheating period 2</v>
+        <v>Phase A — family field work</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>founderTimeline[3].range</v>
+        <v>founderTimeline[1].range</v>
       </c>
       <c r="B92" t="str">
         <v>创始人故事 / 年表</v>
@@ -2512,7 +2512,7 @@
         <v>label</v>
       </c>
       <c r="D92" t="str">
-        <v>Nov 2020 — Jul 2021</v>
+        <v>Mar 2018 — Jul 2020</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>founderTimeline[3].label</v>
+        <v>founderTimeline[1].label</v>
       </c>
       <c r="B93" t="str">
         <v>创始人故事 / 年表</v>
@@ -2535,7 +2535,7 @@
         <v>label</v>
       </c>
       <c r="D93" t="str">
-        <v>Exorcism period 1</v>
+        <v>Cheating Period 1</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>founderTimeline[4].range</v>
+        <v>founderTimeline[2].range</v>
       </c>
       <c r="B94" t="str">
         <v>创始人故事 / 年表</v>
@@ -2558,7 +2558,7 @@
         <v>label</v>
       </c>
       <c r="D94" t="str">
-        <v>Jul 2021 — Apr 2022</v>
+        <v>Jul 2020 — Nov 2020</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>founderTimeline[4].label</v>
+        <v>founderTimeline[2].label</v>
       </c>
       <c r="B95" t="str">
         <v>创始人故事 / 年表</v>
@@ -2581,7 +2581,7 @@
         <v>label</v>
       </c>
       <c r="D95" t="str">
-        <v>Exorcism 2 &amp; high-level revealing</v>
+        <v>Cheating period 2</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>founderTimeline[5].range</v>
+        <v>founderTimeline[3].range</v>
       </c>
       <c r="B96" t="str">
         <v>创始人故事 / 年表</v>
@@ -2604,7 +2604,7 @@
         <v>label</v>
       </c>
       <c r="D96" t="str">
-        <v>Dec 2023 — Jan 2025</v>
+        <v>Nov 2020 — Jul 2021</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>founderTimeline[5].label</v>
+        <v>founderTimeline[3].label</v>
       </c>
       <c r="B97" t="str">
         <v>创始人故事 / 年表</v>
@@ -2627,7 +2627,7 @@
         <v>label</v>
       </c>
       <c r="D97" t="str">
-        <v>Qing Xiaoxian (C2) · Qian Kai (C3)</v>
+        <v>Exorcism period 1</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>founderTimeline[6].range</v>
+        <v>founderTimeline[4].range</v>
       </c>
       <c r="B98" t="str">
         <v>创始人故事 / 年表</v>
@@ -2650,7 +2650,7 @@
         <v>label</v>
       </c>
       <c r="D98" t="str">
-        <v>2025年2月—2026年3月</v>
+        <v>Jul 2021 — Apr 2022</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -2664,7 +2664,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>founderTimeline[6].label</v>
+        <v>founderTimeline[4].label</v>
       </c>
       <c r="B99" t="str">
         <v>创始人故事 / 年表</v>
@@ -2673,7 +2673,7 @@
         <v>label</v>
       </c>
       <c r="D99" t="str">
-        <v>B阶段 · TikTok 直播与灵魂医学档案</v>
+        <v>Exorcism 2 &amp; high-level revealing</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -2687,16 +2687,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>founderStoryIllustrations[0].alt</v>
+        <v>founderTimeline[5].range</v>
       </c>
       <c r="B100" t="str">
-        <v>创始人故事 / 插图说明</v>
+        <v>创始人故事 / 年表</v>
       </c>
       <c r="C100" t="str">
         <v>label</v>
       </c>
       <c r="D100" t="str">
-        <v>Night sky — doorway imagery</v>
+        <v>Dec 2023 — Jan 2025</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -2710,16 +2710,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>founderStoryIllustrations[1].alt</v>
+        <v>founderTimeline[5].label</v>
       </c>
       <c r="B101" t="str">
-        <v>创始人故事 / 插图说明</v>
+        <v>创始人故事 / 年表</v>
       </c>
       <c r="C101" t="str">
         <v>label</v>
       </c>
       <c r="D101" t="str">
-        <v>Cosmos and emergence</v>
+        <v>Qing Xiaoxian (C2) · Qian Kai (C3)</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -2733,19 +2733,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>founderStoryIllustrations[2].alt</v>
+        <v>founderTimeline[6].range</v>
       </c>
       <c r="B102" t="str">
-        <v>创始人故事 / 插图说明</v>
+        <v>创始人故事 / 年表</v>
       </c>
       <c r="C102" t="str">
         <v>label</v>
       </c>
       <c r="D102" t="str">
-        <v>Mountain dawn — long journey</v>
+        <v/>
       </c>
       <c r="E102" t="str">
-        <v/>
+        <v>2025年2月—2026年3月</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -2756,19 +2756,19 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>founderStoryIllustrations[3].alt</v>
+        <v>founderTimeline[6].label</v>
       </c>
       <c r="B103" t="str">
-        <v>创始人故事 / 插图说明</v>
+        <v>创始人故事 / 年表</v>
       </c>
       <c r="C103" t="str">
         <v>label</v>
       </c>
       <c r="D103" t="str">
-        <v>Together — family path</v>
+        <v/>
       </c>
       <c r="E103" t="str">
-        <v/>
+        <v>B阶段 · TikTok 直播与灵魂医学档案</v>
       </c>
       <c r="F103" t="str">
         <v/>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>founderStoryIllustrations[4].alt</v>
+        <v>founderStoryIllustrations[0].alt</v>
       </c>
       <c r="B104" t="str">
         <v>创始人故事 / 插图说明</v>
@@ -2788,21 +2788,113 @@
         <v>label</v>
       </c>
       <c r="D104" t="str">
+        <v>Night sky — doorway imagery</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>founderStoryIllustrations[1].alt</v>
+      </c>
+      <c r="B105" t="str">
+        <v>创始人故事 / 插图说明</v>
+      </c>
+      <c r="C105" t="str">
+        <v>label</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Cosmos and emergence</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>founderStoryIllustrations[2].alt</v>
+      </c>
+      <c r="B106" t="str">
+        <v>创始人故事 / 插图说明</v>
+      </c>
+      <c r="C106" t="str">
+        <v>label</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Mountain dawn — long journey</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>founderStoryIllustrations[3].alt</v>
+      </c>
+      <c r="B107" t="str">
+        <v>创始人故事 / 插图说明</v>
+      </c>
+      <c r="C107" t="str">
+        <v>label</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Together — family path</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>founderStoryIllustrations[4].alt</v>
+      </c>
+      <c r="B108" t="str">
+        <v>创始人故事 / 插图说明</v>
+      </c>
+      <c r="C108" t="str">
+        <v>label</v>
+      </c>
+      <c r="D108" t="str">
         <v>Broadcast and field</v>
       </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v/>
-      </c>
-      <c r="G104" t="str">
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
         <v>founderStory2026Content.ts — ** in source = emphasis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -433,7 +433,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>founderStory.collapsePhaseA</v>
+        <v>founderStory.achievementsFeaturePageLink</v>
       </c>
       <c r="B2" t="str">
         <v>创始人故事 / i18n</v>
@@ -442,10 +442,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D2" t="str">
-        <v>✦  Hide Phase A detail  ▲</v>
+        <v>2025 Livestream Achievements</v>
       </c>
       <c r="E2" t="str">
-        <v>✦  收起 A 阶段详情  ▲</v>
+        <v>《2025直播间成就》专题页</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -456,7 +456,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>founderStory.collapsePhaseB</v>
+        <v>founderStory.collapsePhaseA</v>
       </c>
       <c r="B3" t="str">
         <v>创始人故事 / i18n</v>
@@ -465,10 +465,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D3" t="str">
-        <v>✦  Hide Phase B detail  ▲</v>
+        <v>✦  Hide Phase A detail  ▲</v>
       </c>
       <c r="E3" t="str">
-        <v>✦  收起 B 阶段详情  ▲</v>
+        <v>✦  收起 A 阶段详情  ▲</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -479,7 +479,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>founderStory.expandPhaseA</v>
+        <v>founderStory.collapsePhaseB</v>
       </c>
       <c r="B4" t="str">
         <v>创始人故事 / i18n</v>
@@ -488,10 +488,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D4" t="str">
-        <v>✦  Show Phase A chronology &amp; full detail  ▼</v>
+        <v>✦  Hide Phase B detail  ▲</v>
       </c>
       <c r="E4" t="str">
-        <v>✦  展开 A 阶段年表与完整叙事  ▼</v>
+        <v>✦  收起 B 阶段详情  ▲</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -502,7 +502,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>founderStory.expandPhaseB</v>
+        <v>founderStory.expandPhaseA</v>
       </c>
       <c r="B5" t="str">
         <v>创始人故事 / i18n</v>
@@ -511,10 +511,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D5" t="str">
-        <v>✦  Show Phase B chronology &amp; full detail  ▼</v>
+        <v>✦  Show Phase A chronology &amp; full detail  ▼</v>
       </c>
       <c r="E5" t="str">
-        <v>✦  展开 B 阶段年表与完整叙事  ▼</v>
+        <v>✦  展开 A 阶段年表与完整叙事  ▼</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -525,7 +525,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>founderStory.phaseAUmbrellaCaption</v>
+        <v>founderStory.expandPhaseB</v>
       </c>
       <c r="B6" t="str">
         <v>创始人故事 / i18n</v>
@@ -534,10 +534,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v>Overall window for family field work (Phase A). Sub-stages A1–A5 below: date line first, then narrative.</v>
+        <v>✦  Show Phase B chronology &amp; full detail  ▼</v>
       </c>
       <c r="E6" t="str">
-        <v>A 阶段总览时间窗（家庭田野）。以下 A1–A5：每条先时间线，再正文，仅保留小节标题 A1、A2…</v>
+        <v>✦  展开 B 阶段年表与完整叙事  ▼</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -548,7 +548,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>founderStory.storylineClipLead</v>
+        <v>founderStory.phaseAUmbrellaCaption</v>
       </c>
       <c r="B7" t="str">
         <v>创始人故事 / i18n</v>
@@ -557,10 +557,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D7" t="str">
-        <v>**Stage {{stage}}** on the original storyline: companion image plus the same YouTube session (embedded below). For context see</v>
+        <v>Overall window for family field work (Phase A). Sub-stages A1–A5 below: date line first, then narrative.</v>
       </c>
       <c r="E7" t="str">
-        <v>与旧站叙事 **第 {{stage}} 阶段**对应：配图 + 同一则 YouTube（下方嵌入）。完整语境见</v>
+        <v>A 阶段总览时间窗（家庭田野）。以下 A1–A5：每条先时间线，再正文，仅保留小节标题 A1、A2…</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -571,7 +571,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>founderStory.storylineClipPageLink</v>
+        <v>founderStory.storylineClipLead</v>
       </c>
       <c r="B8" t="str">
         <v>创始人故事 / i18n</v>
@@ -580,10 +580,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D8" t="str">
-        <v>Storyline of Woos</v>
+        <v>**Stage {{stage}}** on the original storyline: companion image plus the same YouTube session (embedded below). For context see</v>
       </c>
       <c r="E8" t="str">
-        <v>《Storyline of Woos》</v>
+        <v>与旧站叙事 **第 {{stage}} 阶段**对应：配图 + 同一则 YouTube（下方嵌入）。完整语境见</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -594,19 +594,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>founderStory.storylineYoutubeIframeTitle</v>
+        <v>founderStory.storylineClipPageLink</v>
       </c>
       <c r="B9" t="str">
         <v>创始人故事 / i18n</v>
       </c>
       <c r="C9" t="str">
-        <v>heading</v>
+        <v>paragraph / other</v>
       </c>
       <c r="D9" t="str">
-        <v>Storyline of Woos — Stage {{stage}} recording</v>
+        <v>Storyline of Woos</v>
       </c>
       <c r="E9" t="str">
-        <v>Storyline of Woos — 第 {{stage}} 阶段录像</v>
+        <v>《Storyline of Woos》</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -617,39 +617,39 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>founderStorySurfaceCopy.heroNamesLine</v>
+        <v>founderStory.storylineYoutubeIframeTitle</v>
       </c>
       <c r="B10" t="str">
-        <v>创始人故事 / 英雄区副标题</v>
+        <v>创始人故事 / i18n</v>
       </c>
       <c r="C10" t="str">
-        <v>label</v>
+        <v>heading</v>
       </c>
       <c r="D10" t="str">
-        <v>John Long Woo · Caros · Sam</v>
+        <v>Storyline of Woos — Stage {{stage}} recording</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>Storyline of Woos — 第 {{stage}} 阶段录像</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>founderStorySurfaceCopy — FounderStoryView chrome</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>founderStorySurfaceCopy.backToAbout</v>
+        <v>founderStorySurfaceCopy.heroNamesLine</v>
       </c>
       <c r="B11" t="str">
-        <v>创始人故事 / 返回</v>
+        <v>创始人故事 / 英雄区副标题</v>
       </c>
       <c r="C11" t="str">
-        <v>button / link</v>
+        <v>label</v>
       </c>
       <c r="D11" t="str">
-        <v>← Organization overview</v>
+        <v>John Long Woo · Caros · Sam</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -663,16 +663,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>founderStorySurfaceCopy.legacyTimelineLink</v>
+        <v>founderStorySurfaceCopy.backToAbout</v>
       </c>
       <c r="B12" t="str">
-        <v>创始人故事 / 页脚外链</v>
+        <v>创始人故事 / 返回</v>
       </c>
       <c r="C12" t="str">
         <v>button / link</v>
       </c>
       <c r="D12" t="str">
-        <v>Earlier staged timeline on the legacy site</v>
+        <v>← Organization overview</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -686,19 +686,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>founderStorySurfaceCopy.achievementsFeaturePageLink</v>
+        <v>founderStorySurfaceCopy.legacyTimelineLink</v>
       </c>
       <c r="B13" t="str">
-        <v>创始人故事 / Phase B 内链（替换 {{%ACH%}}）</v>
+        <v>创始人故事 / 页脚外链</v>
       </c>
       <c r="C13" t="str">
         <v>button / link</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>Earlier staged timeline on the legacy site</v>
       </c>
       <c r="E13" t="str">
-        <v>《2025直播间成就》专题页</v>
+        <v/>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -2167,7 +2167,7 @@
         <v>heading</v>
       </c>
       <c r="D77" t="str">
-        <v/>
+        <v>Phase B — February 2025 through March 2026</v>
       </c>
       <c r="E77" t="str">
         <v>B阶段：2025年2月至2026年3月</v>
@@ -2176,7 +2176,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.title</v>
       </c>
     </row>
     <row r="78">
@@ -2190,7 +2190,7 @@
         <v>heading</v>
       </c>
       <c r="D78" t="str">
-        <v/>
+        <v>Livestream scale and documented outcomes</v>
       </c>
       <c r="E78" t="str">
         <v>直播间规模与成就记录</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block0.title</v>
       </c>
     </row>
     <row r="79">
@@ -2213,7 +2213,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D79" t="str">
-        <v/>
+        <v>From **19 February 2025** through **24 December 2025**, **Caros** hosted **265** sessions on **TikTok Live** and achieved **extraordinary outcomes** in the broadcast field. Full documentation and links: {{%ACH%}}</v>
       </c>
       <c r="E79" t="str">
         <v>从 **2025年2月19日** 至 **12月24日**，**Caros** 在 **TikTok** 上总共进行了 **265 场直播**；在直播间取得了 **超凡的成就**。完整记录与链接见：{{%ACH%}}</v>
@@ -2222,7 +2222,7 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block0.text</v>
       </c>
     </row>
     <row r="80">
@@ -2236,7 +2236,7 @@
         <v>heading</v>
       </c>
       <c r="D80" t="str">
-        <v/>
+        <v>Master Spirits, hybrid spirits, and remote capacity</v>
       </c>
       <c r="E80" t="str">
         <v>Master Spirit、混合灵与远程能力</v>
@@ -2245,7 +2245,7 @@
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block1.title</v>
       </c>
     </row>
     <row r="81">
@@ -2259,7 +2259,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D81" t="str">
-        <v/>
+        <v>A great many **Master Spirits** and **hybrid spirits** reached out to us as father and sons, revealing that the spirit world includes order at the levels of **administrators** and **creator-class** structure. **Master Spirits** gave us extensive support and **unusual abilities**, so that **Caros**, **while in China**, could **remotely regulate** attached spirits on **hosts in North America** on the far side of the globe.</v>
       </c>
       <c r="E81" t="str">
         <v>大量的 **Master Spirit** 以及 **混合灵（hybrid spirit）** 与我们父子联系，让我们知道灵魂世界竟然有 **管理者** 与 **造物主** 层面的秩序。**Master Spirit** 给我们很多帮助与 **特别的超常力量**，使 **Caros** 在中国就可以 **远程制约** 远在地球另一端北美附体的鬼魂。</v>
@@ -2268,7 +2268,7 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block1.text</v>
       </c>
     </row>
     <row r="82">
@@ -2282,7 +2282,7 @@
         <v>heading</v>
       </c>
       <c r="D82" t="str">
-        <v/>
+        <v>How Phase A attachments were arranged</v>
       </c>
       <c r="E82" t="str">
         <v>关于 A 阶段附体安排的说明</v>
@@ -2291,7 +2291,7 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block2.title</v>
       </c>
     </row>
     <row r="83">
@@ -2305,7 +2305,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D83" t="str">
-        <v/>
+        <v>**Most importantly**, we were told: every attached spirit on us during **Phase A** was **deliberately placed** by **Master Spirits**; clearing those presences was **authorized to serve as research material**.</v>
       </c>
       <c r="E83" t="str">
         <v>**最重要的是**，我们被告知：**A 阶段** 在我们身上附体的鬼魂都是被 **Master Spirit** **刻意安排** 进来的；这些附体之灵被清除是 **被许可作为研究使用** 的。</v>
@@ -2314,7 +2314,7 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block2.text</v>
       </c>
     </row>
     <row r="84">
@@ -2328,7 +2328,7 @@
         <v>heading</v>
       </c>
       <c r="D84" t="str">
-        <v/>
+        <v>Illness, deception, and narrative as part of the plan</v>
       </c>
       <c r="E84" t="str">
         <v>计划中的病痛与叙事</v>
@@ -2337,7 +2337,7 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block3.title</v>
       </c>
     </row>
     <row r="85">
@@ -2351,7 +2351,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D85" t="str">
-        <v/>
+        <v>The **suffering**, **deception**, and **taunting storylines** were also part of their plan—so we could learn their **operating style** and **disposition**.</v>
       </c>
       <c r="E85" t="str">
         <v>所有的 **病痛折磨**、**欺骗**、**戏弄性的故事** 也是他们计划的一部分，让我们了解其 **行事风格** 与 **性格秉性**。</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block3.text</v>
       </c>
     </row>
     <row r="86">
@@ -2374,7 +2374,7 @@
         <v>heading</v>
       </c>
       <c r="D86" t="str">
-        <v/>
+        <v>Understanding Master Spirit character</v>
       </c>
       <c r="E86" t="str">
         <v>对 Master Spirit 品性的认识</v>
@@ -2383,7 +2383,7 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block4.title</v>
       </c>
     </row>
     <row r="87">
@@ -2397,7 +2397,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D87" t="str">
-        <v/>
+        <v>That also showed us clearly: **Master Spirits** are **not** **angel-good** in the way we imagined; the help offered earlier was **not** driven by **kindness** but by **assignments** from the **Universal Matrix of Meta Awareness**. The **Phase A** stories convey the **temperament of the Master Spirit team** in depth.</v>
       </c>
       <c r="E87" t="str">
         <v>这也让我们完整认识到：**Master Spirit** 并非像我们想象中的 **天使般的善良**；先前提供的帮助 **并非出于善良**，而是 **万有元神母体** 给他们安排的工作。大家可以通过 **A 阶段故事** 充分体会 **Master Spirit 团队的性格属性**。</v>
@@ -2406,7 +2406,7 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block4.text</v>
       </c>
     </row>
     <row r="88">
@@ -2420,7 +2420,7 @@
         <v>heading</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>Spirit Medicine and video archives</v>
       </c>
       <c r="E88" t="str">
         <v>灵魂医学与影像档案</v>
@@ -2429,7 +2429,7 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block5.title</v>
       </c>
     </row>
     <row r="89">
@@ -2443,7 +2443,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D89" t="str">
-        <v/>
+        <v>During this period **Spirit Medicine was formally established**; we produced **part of** the **Woos Spirit Medicine** and **Universal Matrix of Meta Awareness** video archives.</v>
       </c>
       <c r="E89" t="str">
         <v>在此期间，**正式创建了灵魂医学**；拍摄了 **《吴氏灵魂医学》** 与 **《万有元神母体》** 系列视频档案中的 **一部分视频**。</v>
@@ -2452,7 +2452,7 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>founderStory2026Content.ts — ** in source = emphasis</v>
+        <v>Phase B: EN = content file; 中文 = zh.ts → founderStory.phaseB.block5.text</v>
       </c>
     </row>
     <row r="90">

--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -529,10 +529,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v>I, John LONG WOO, and my two sons Caros and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the **first door opener** in the spiritual realm and the **first explorer** of the truth of spirit life.</v>
+        <v>I, John LONG WOO, and my two sons Caros and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of spirit life.</v>
       </c>
       <c r="E6" t="str">
-        <v>我， John LONG WOO, 和我的两个儿子Caros和Sam，我们父子三人，与灵魂世界有太多传奇的故事。这些经历造就我们是 **灵魂世界首位开门者 **，并且是 **灵魂生命真相的首位探索者 **</v>
+        <v>我， John LONG WOO, 和我的两个儿子Caros和Sam，我们父子三人，与灵魂世界有太多传奇的故事。这些经历造就我们是灵魂世界首位开门者，并且是灵魂生命真相的首位探索者。</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -598,10 +598,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D9" t="str">
-        <v>A living person is composed of both the **physical body** and the **spirit (soul)**. After death, the spirit becomes a **ghost (spirit ghost)**. For the **billions** of them, the only means of survival is to **attach to human beings** and obtain energy. This leads to global diseases such as **epilepsy**, **depression**, **schizophrenia**, and **somatic symptoms**. Through **managing spirits (ghosts) by master spirits**, these conditions can be rapidly improved. From this work we created **Spirit Medicine**.</v>
+        <v>A living person is composed of both the physical body and the spirit (soul). After death, the spirit becomes a ghost (spirit ghost). But for the billions of ghosts, the only means of survival is to obtain energy by attaching to human beings. Ghost attachment causes many diseases, such as epilepsy, depression, schizophrenia, and somatic symptom disorders. With the help of master spirits, these conditions can be rapidly improved. For this we created **Woos Spirit Medicine**.</v>
       </c>
       <c r="E9" t="str">
-        <v>人活着时是由**肉体**和**灵体**组成的，死后灵体成为了**鬼魂**（spirit ghost），但是数以**几十亿**的鬼魂（spirit ghost）生存的唯一手段是通过**附体人类**获得能量，导致了疾病，例如**癫痫**、**抑郁**、**精分**、**躯体化障碍**。在高级控制灵的帮助下，这些病症可以迅速被改善。并且我们创建了**吴氏灵魂医学**。</v>
+        <v>人活着时是由肉体和灵体组成的，死后灵体成为了鬼魂（spirit ghost），但是数以几十亿的鬼魂生存的唯一手段是通过附体人类获得能量。鬼魂附体导致了很多疾病，例如：癫痫、抑郁、精分、躯体化障碍。在高级控制灵的帮助下，这些病症可以迅速被改善。为此我们创建了**吴氏灵魂医学**。</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -647,7 +647,7 @@
         <v>Further documentation appears in the **Woos Record of Soul** and the **Woos Spirit Medicine** video archives.</v>
       </c>
       <c r="E11" t="str">
-        <v>详细内容在**吴氏灵体档案**和**吴氏灵魂医学视频档案**。</v>
+        <v>详细内容在**吴氏灵体档案**和**吴氏灵魂医学**视频档案。</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -690,10 +690,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D13" t="str">
-        <v>The **Spirit Realm** has governors — tremendous **master spirits**, upgraded from ordinary **C1 spirit ghosts** through the **Universal Matrix of Meta Awareness** (spirit realm has governor, who are tremendous master spirits, upgraded from C1 spirit ghost by Universal Matrix of Meta Awareness).</v>
+        <v>The Spirit Realm has governors — tremendous master spirits (master spirit), upgraded from ordinary spirit ghosts through the **Universal Matrix of Meta Awareness**.</v>
       </c>
       <c r="E13" t="str">
-        <v>灵魂世界有统御者，他们是数量多的**高级控制灵**（master spirit），是被**万有元神母体**从普通鬼魂中挑选并升级而来</v>
+        <v>灵魂世界有统御者，他们是数量多的高级控制灵（master spirit），是被**万有元神母体**从普通鬼魂中挑选并升级而来</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -736,10 +736,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D15" t="str">
-        <v>The **Universal Matrix of Meta Awareness** is the **true creator**. Our **13.8-billion-year universe** is a part of **its body**.</v>
+        <v>**Universal Matrix of Meta Awareness** is the true creator. Our 13.8-billion-year universe is part of its body. Further documentation appears in the **Universal Matrix of Meta Awareness** video archive.</v>
       </c>
       <c r="E15" t="str">
-        <v>**万有元神母体**（Universal Matrix of Meta Awareness）是真实的造物主，我们**130亿年**的宇宙是它**身体的一部分**</v>
+        <v>**万有元神母体（Universal Matrix of Meta Awareness）**是真实的造物主，我们130 亿年的宇宙是它身体的一部分。更多文献见**万有元神母体（Universal Matrix of Meta Awareness）**视频档案。</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -830,10 +830,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D19" t="str">
-        <v>In this phase, we mainly fought the **attached spirits (ghosts) of different levels** parasitizing our bodies — including the **C1-level**  ghost  (Hui'an), the **C2-level** ghost **Qing Xiaoxian**, and the **C3-level** ghost**Qian Kai**. They caused **various illnesses across our entire family**.</v>
+        <v>In this phase, we mainly fought the attached spirits (ghosts) of different levels parasitizing our bodies — including Hui'an (C1 level), Qing Xiaoxian (C2 level), and Qian Kai (C3 level). They caused various illnesses across our entire family.</v>
       </c>
       <c r="E19" t="str">
-        <v>在这个阶段，主要是在和我们体内寄生的**不同级别的鬼魂**作斗争，他们造就了**我们全家的各种病痛**。其中包括鬼魂惠安（C1级别）、鬼魂**青小仙**（C2级别）、鬼魂**钱凯**（C3级别）。</v>
+        <v>在这个阶段，主要是在和我们体内寄生的不同级别的鬼魂作斗争，他们造就了我们全家的各种病痛。其中包括鬼魂惠安（C1级别）、鬼魂青小仙（C2级别）、鬼魂钱凯（C3级别）。</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -876,10 +876,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D21" t="str">
-        <v>We fought only for **self-rescue** — trying and researching every possible method to **kill** them. In the process of harming and destroying them, we learned the **matter properties, physiological and physical properties of ghost bodies**, and communicated through **epileptic discharge**, **auditory hallucination sounds**, **consciousness dialogue**, **consciousness control**, and other modes — building a verified picture of the spirit world.</v>
+        <v>We fought only for self-rescue — trying and researching every possible method to kill them. In the process of harming and destroying them, we learned the matter properties, physiological and physical properties of ghost bodies, and communicated through epileptic discharge, auditory hallucination sounds, consciousness dialogue, consciousness control, and other modes — building a verified picture of the spirit world.</v>
       </c>
       <c r="E21" t="str">
-        <v>我们只是为了**自救**而努力尝试和研究用各种方法去**杀死**他们。在杀死杀伤他们的过程中我们了解了**鬼魂身体的物质，生理属性和物理属性**，并且在这个过程中，我们与鬼魂使用**癫痫放电**、**幻听**、**意识对话**、**意识控制**等各种方式进行交流，了解了灵魂世界大量的真实信息。</v>
+        <v>我们只是为了自救而努力尝试和研究用各种方法去杀死他们。在杀死杀伤他们的过程中我们了解了鬼魂身体的物质，生理属性和物理属性，并且在这个过程中，我们与鬼魂使用癫痫放电、幻听、意识对话、意识控制等各种方式进行交流，了解了灵魂世界大量的真实信息。</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -922,10 +922,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D23" t="str">
-        <v>Our greatest regret in **Phase A** is that we did **not** engage with attached spirits on **other people** outside our family, or those in **other countries**.</v>
+        <v>Our greatest regret in Phase A is that we did not engage with attached spirits on other people outside our family, or those in other countries.</v>
       </c>
       <c r="E23" t="str">
-        <v>这个阶段最大的遗憾是，我们没有与**外界其他人**和**其他国家**的附体鬼魂进行交流。</v>
+        <v>这个阶段最大的遗憾是，我们没有与外界其他人和其他国家的附体鬼魂进行交流。</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1060,10 +1060,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D29" t="str">
-        <v>During this period, the **C1 spirit ghost** in my body used the way of releasing **high voltage electrostatic** in drinks and wine to change the taste of drinks, aimed to fabricate a series of scientific phenomena and laws, which would finally lead to the proof of the existence of **Buddhism**. The details are complicated to explain clearly in words.</v>
+        <v>During this period, the C1 spirit ghost in my body used the way of releasing high voltage electrostatic in drinks and wine to change the taste of drinks, aimed to fabricate a series of scientific phenomena and laws, which would finally lead to the proof of the existence of Buddhism. The details are complicated to explain clearly in words.</v>
       </c>
       <c r="E29" t="str">
-        <v>在此期间，我体内的**C1级别鬼魂**通过在饮料和酒中释放**高压静电**的方式改变饮料口感，目的是伪造一系列科学现象和规律，最终导向**佛教存在**的"证明"。详情过于复杂，难以用文字完全说清楚。</v>
+        <v>在此期间，我体内的C1级别鬼魂通过在饮料和酒中释放高压静电的方式改变饮料口感，目的是伪造一系列科学现象和规律，最终导向佛教存在的"证明"。详情过于复杂，难以用文字完全说清楚。</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1178,7 +1178,7 @@
         <v>During this period, Hui 'an, a C1-level ghost in my body, used the way of epileptic seizures to disguise himself as the three great Buddhists in different periods, and finally let my two sons and I convert to Buddhism under the pretext of conveying the divine will. This is actually a big joke, playing tricks on our family like monkeys, which is also the standard paranoia in schizophrenia. However, in the process of cheating and playing tricks, we also exchanged a lot of philosophical cognition and knowledge with the ghost Huian.</v>
       </c>
       <c r="E34" t="str">
-        <v>在此期间，我体内的**C1级别鬼魂**使用**癫痫发作**的方式，分时段伪装成**佛教三大菩萨**，假借传达神旨，最终让我和两个儿子皈依了**佛教**。这其实是一个大笑话，把我们全家当像猴子一样耍弄，这也是精神分裂症中标准的妄想症。然而，在欺骗和耍弄过程中，我们与鬼魂惠安也交流了大量的哲学认知与知识。</v>
+        <v>在此期间，我体内的C1级别鬼魂使用癫痫发作的方式，分时段伪装成佛教三大菩萨，假借传达神旨，最终让我和两个儿子皈依了佛教。这其实是一个大笑话，把我们全家当像猴子一样耍弄，这也是精神分裂症中标准的妄想症。然而，在欺骗和耍弄过程中，我们与鬼魂惠安也交流了大量的哲学认知与知识。</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1267,10 +1267,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D38" t="str">
-        <v>At **Nov 15, 2020**, the **real identities** of spirit ghosts inside us and their tricks were finally **debunked**. In great fear and anger, we want to **exorcise** them. After many failures using traditional ways, we recalled that they always forbade us to touch any **strong magnets** with various excuses in previous communications. So we started using **magnets** to hurt them.</v>
+        <v>At Nov 15, 2020, the real identities of spirit ghosts inside us and their tricks were finally debunked. In great fear and anger, we want to exorcise them. After many failures using traditional ways, we recalled that they always forbade us to touch any strong magnets with various excuses in previous communications. So we started using magnets to hurt them.</v>
       </c>
       <c r="E38" t="str">
-        <v>**2020年11月15日**，我们体内鬼魂的**真实身份**及其把戏终于被**揭穿**。在极度恐惧和愤怒中，我们想要**驱逐**它们。在多次尝试传统方法失败后，我们回想起它们在之前交流中总是以各种借口**禁止**我们接触**强磁铁**。于是我们开始使用磁铁来**伤害**它们。</v>
+        <v>2020年11月15日，我们体内鬼魂的真实身份及其把戏终于被揭穿。在极度恐惧和愤怒中，我们想要驱逐它们。在多次尝试传统方法失败后，我们回想起它们在之前交流中总是以各种借口禁止我们接触强磁铁。于是我们开始使用磁铁来伤害它们。</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D39" t="str">
-        <v>A few days later, the spirit ghost inside my **elder son** couldn't stand it and **left first**. Then after a **month and a half**, the spirit ghost inside my **younger son** also left due to the same reason. But the spirit ghost in my body was unable to leave even it was already slightly injured, it made me puzzled.</v>
+        <v>A few days later, the spirit ghost inside my elder son couldn't stand it and left first. Then after a month and a half, the spirit ghost inside my younger son also left due to the same reason. But the spirit ghost in my body was unable to leave even it was already slightly injured, it made me puzzled.</v>
       </c>
       <c r="E39" t="str">
-        <v>几天后，我**大儿子**体内的鬼魂首先忍受不了而**离开**。大约一个半月后，我**小儿子**体内的鬼魂也因同样的原因离开了。但我体内的鬼魂即使已经受轻伤也无法离开，这让我困惑不解。</v>
+        <v>几天后，我大儿子体内的鬼魂首先忍受不了而离开。大约一个半月后，我小儿子体内的鬼魂也因同样的原因离开了。但我体内的鬼魂即使已经受轻伤也无法离开，这让我困惑不解。</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -1313,10 +1313,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D40" t="str">
-        <v>I found out that using a **strong electrostatic field** could greatly weaken it from discharging, and my **epilepsy** was eliminated immediately once it happens. But the spirit ghost was still inside me and continued **played hide and seek** with me.</v>
+        <v>I found out that using a strong electrostatic field could greatly weaken it from discharging, and my epilepsy was eliminated immediately once it happens. But the spirit ghost was still inside me and continued played hide and seek with me.</v>
       </c>
       <c r="E40" t="str">
-        <v>我发现使用**强静电场**可以大幅削弱它的放电能力，而我的**癫痫**在这种情况发生时会立即消除。但鬼魂仍然在我体内，继续与我**捉迷藏**。</v>
+        <v>我发现使用强静电场可以大幅削弱它的放电能力，而我的癫痫在这种情况发生时会立即消除。但鬼魂仍然在我体内，继续与我捉迷藏。</v>
       </c>
       <c r="F40" t="str">
         <v/>
@@ -1405,10 +1405,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D44" t="str">
-        <v>During this stage, several ways of **interfering, hurting and killing C1 spirit ghost** were found and confirmed.</v>
+        <v>During this stage, several ways of interfering, hurting and killing C1 spirit ghost were found and confirmed.</v>
       </c>
       <c r="E44" t="str">
-        <v>在这个阶段，找到并确认了几种**干扰、伤害和杀死C1级别鬼魂**的方法。</v>
+        <v>在这个阶段，找到并确认了几种干扰、伤害和杀死C1级别鬼魂的方法。</v>
       </c>
       <c r="F44" t="str">
         <v/>
@@ -1428,10 +1428,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D45" t="str">
-        <v>The limitation of magnet therapy aroused the interest of an advanced spirit **(not a master spirit)** who died in China about 1500 years ago. It quietly participated in the process of exploring how to expel and kill the C1-level spirit ghost Huian. In this process, it used the way of consciousness transmission to give me hints and inspiration, and also manipulated the behavior of Hui 'an, and finally let me know how to kill and expel huian accurately and efficiently.</v>
+        <v>The limitation of magnet therapy aroused the interest of an advanced spirit (not a master spirit) who died in China about 1500 years ago. It quietly participated in the process of exploring how to expel and kill the C1-level spirit ghost Huian. In this process, it used the way of consciousness transmission to give me hints and inspiration, and also manipulated the behavior of Hui 'an, and finally let me know how to kill and expel huian accurately and efficiently.</v>
       </c>
       <c r="E45" t="str">
-        <v>磁铁疗法的局限性引起了一位在中国去世约1500年的高级灵**（不是高级控制灵）**的兴趣。它悄悄参与了探索如何驱逐和杀死C1级别鬼魂惠安的过程。在此过程中，它使用意识传输的方式给我提示和灵感，同时也操控C1级别鬼魂惠安的行为，最终让我知道了如何精确高效地杀死和驱逐C1级别鬼魂</v>
+        <v>磁铁疗法的局限性引起了一位在中国去世约1500年的高级灵（不是高级控制灵）的兴趣。它悄悄参与了探索如何驱逐和杀死C1级别鬼魂惠安的过程。在此过程中，它使用意识传输的方式给我提示和灵感，同时也操控C1级别鬼魂惠安的行为，最终让我知道了如何精确高效地杀死和驱逐C1级别鬼魂</v>
       </c>
       <c r="F45" t="str">
         <v/>
@@ -1451,10 +1451,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D46" t="str">
-        <v>As a father, I pester, fight and coexist with Hui 'an, every day, forming a subtle relationship that * * is both an enemy and a friend**. In the process of hurting ghosts, we also exchanged a lot of knowledge about spirit-related information. Finally, the advanced spirit appeared and showed his extraordinary ability. It explained all kinds of puzzles in the past year and taught me more about the spiritual realm. Then it left my body and quickly disappeared</v>
+        <v>As a father, I pester, fight and coexist with Hui 'an every day, forming a subtle relationship that is both enemy and friend. In the process of hurting ghosts, we also exchanged a lot of knowledge about spirit-related information. Finally, the advanced spirit appeared and demonstrated extraordinary ability. It explained various puzzles from the past year and taught me more about the spiritual realm, then left my body and vanished quickly.</v>
       </c>
       <c r="E46" t="str">
-        <v>做父亲的我每天与C1级别鬼魂惠安纠缠、搏斗、共存，形成了一种**既是敌人又是朋友**的微妙关系。在伤害鬼魂的过程中，我们也交流了大量关于灵魂相关信息的知识。最终，这个高级领现身并展示了其非凡能力。它解释了过去一年中的各种困惑，并教了我更多灵魂世界的知识，然后它离开了我的身体并迅速消失</v>
+        <v>做父亲的我每天与C1级别鬼魂惠安纠缠、搏斗、共存，形成了一种既是敌人又是朋友的微妙关系。在伤害鬼魂的过程中，我们也交流了大量关于灵魂相关信息的知识。最终，这个高级领现身并展示了其非凡能力。它解释了过去一年中的各种困惑，并教了我更多灵魂世界的知识，然后它离开了我的身体并迅速消失</v>
       </c>
       <c r="F46" t="str">
         <v/>
@@ -1543,10 +1543,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D50" t="str">
-        <v>In December 2023, as a father, I was once again attached by a **C2 level * * ghost, Qing Xiaoxian. During the **1700** years of its existence as a ghost, it swallowed about **5000 to 10000** other spirits ghosts, thus having a very huge body. It turned our house into a haunted house, and created a number of Remote port organs (RPO) attached to two sons, with whom the main body could communicate remotely</v>
+        <v>In December 2023, as a father, I was once again attached by a C2-level ghost, Qing Xiaoxian. During its 1,700 years as a ghost, it swallowed about 5,000 to 10,000 other spirits, thus forming a very large body. It turned our house into a haunted house and created multiple Remote Port Organs (RPO) attached to both sons; the main body could communicate with them remotely.</v>
       </c>
       <c r="E50" t="str">
-        <v>2023年12月，作为父亲的我又被一个**C2级别**的鬼魂青小仙再次附体。在它作为鬼魂存在的**1700**年间，吞噬了大约**5000到10000**个其他鬼魂，从而拥有了一个十分庞大的躯体。它将吴氏家变成了一座鬼屋，并制造出多个分身（RPO）附身于两个儿子身上，其身体主体能够与这些分身进行远程交流</v>
+        <v>2023年12月，作为父亲的我又被一个C2级别的鬼魂青小仙再次附体。在它作为鬼魂存在的1700年间，吞噬了大约5000到10000个其他鬼魂，从而拥有了一个十分庞大的躯体。它将吴氏家变成了一座鬼屋，并制造出多个分身（RPO）附身于两个儿子身上，其身体主体能够与这些分身进行远程交流</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -1566,10 +1566,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D51" t="str">
-        <v>In my body, this ghost has caused many manifestations such as **schizophrenia, bipolar disorder, epilepsy and somatization**. It also attacked my heart with extremely powerful current, and had symptoms of **acute heart failure**. In two sons, it caused **chronic fatigue, depression, pain disorder and irritable bowel syndrome, as well as other somatization symptoms**</v>
+        <v>In my body, this ghost has caused many manifestations such as schizophrenia, bipolar disorder, epilepsy and somatization. It also attacked my heart with extremely powerful current, and had symptoms of acute heart failure. In two sons, it caused chronic fatigue, depression, pain disorder and irritable bowel syndrome, as well as other somatization symptoms</v>
       </c>
       <c r="E51" t="str">
-        <v>在我身上，这个鬼魂引发了**精神分裂症、躁郁症、癫痫和躯体化症状**等多种表现。它还用极其强大的电流攻击过我的心脏，出现过**急性心衰**的症状。在两个儿子身上，它导致了**慢性疲劳、抑郁、疼痛障碍和肠易激综合征，以及其他躯体化症状**</v>
+        <v>在我身上，这个鬼魂引发了精神分裂症、躁郁症、癫痫和躯体化症状等多种表现。它还用极其强大的电流攻击过我的心脏，出现过急性心衰的症状。在两个儿子身上，它导致了慢性疲劳、抑郁、疼痛障碍和肠易激综合征，以及其他躯体化症状</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -1589,10 +1589,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D52" t="str">
-        <v>We continued to refine **exorcism and ghost-elimination** techniques and ultimately **successfully destroyed** this ghost.</v>
+        <v>We continued to refine exorcism and ghost-elimination techniques and ultimately successfully destroyed this ghost.</v>
       </c>
       <c r="E52" t="str">
-        <v>我们继续完善**驱鬼和杀鬼**技术，最终成功地**消灭**了这个鬼魂。</v>
+        <v>我们继续完善驱鬼和杀鬼技术，最终成功地消灭了这个鬼魂。</v>
       </c>
       <c r="F52" t="str">
         <v/>
@@ -1612,10 +1612,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D53" t="str">
-        <v>From September 2024 to January 2025, as a father, I was once again attached by a C3-level spirit ghost, Qian Kai. Its body density is * * much higher than **C2 ghost qingxiaoxian. The higher the density of a ghost's body, the stronger its ability. Therefore, Qian Kai's thinking control and pathogenic ability are stronger. We also continued to save ourselves and killed the ghost</v>
+        <v>From September 2024 to January 2025, as a father, I was again attached by a C3-level ghost, Qian Kai. Qian Kai's density was far higher than the C2-level Qing Xiaoxian. The higher a ghost's density, the stronger its ability—so Qian Kai's thought-control and pathogenic power were stronger as well. We continued self-rescue and eliminated this ghost.</v>
       </c>
       <c r="E53" t="str">
-        <v>*2024年9月到2025年1月，做父亲的我再次被一个C3级别的鬼魂钱凯附体。钱凯的身体密度要**远高于**C2级别的青小仙。鬼魂的身体密度越高能力越强。因此，钱凯的思维控制和致病能力也越强。我们同样继续自救，杀死了这个鬼魂</v>
+        <v>*2024年9月到2025年1月，做父亲的我再次被一个C3级别的鬼魂钱凯附体。钱凯的身体密度要远高于C2级别的青小仙。鬼魂的身体密度越高能力越强。因此，钱凯的思维控制和致病能力也越强。我们同样继续自救，杀死了这个鬼魂</v>
       </c>
       <c r="F53" t="str">
         <v/>
@@ -1681,10 +1681,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D56" t="str">
-        <v>In this phase, **Caros** communicated with a large number of **attached ghosts** in North America through **TikTok live streams**, completely confirming all the **spirit world truths** we obtained in **Phase A**. With the help of **master spirits**, Caros obtained the **superpower to remotely control attached ghosts** in North America. This superpower is the foundation upon which we built **ASRA**.</v>
+        <v>In this phase, Caros communicated with a large number of attached ghosts in North America through TikTok live streams, completely confirming all the spirit world truths we obtained in Phase A. With the help of master spirits, Caros obtained the superpower to remotely control attached ghosts in North America. This superpower is the foundation upon which we built ASRA.</v>
       </c>
       <c r="E56" t="str">
-        <v>在这个阶段，**Caros**通过**TikTok直播间**与北美的大量**附体鬼魂**进行了交流，完全**证实**了A阶段我们获得的所有**灵魂世界真相**。并且在**高级控制灵**的帮助下，Caros获得了**远程控制**北美附体鬼魂的**超能力**。这种超能力正是我们建设**ASRA**的基础。</v>
+        <v>在这个阶段，Caros通过TikTok直播间与北美的大量附体鬼魂进行了交流，完全证实了A阶段我们获得的所有灵魂世界真相。并且在高级控制灵的帮助下，Caros获得了远程控制北美附体鬼魂的超能力。这种超能力正是我们建设ASRA的基础。</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -1727,10 +1727,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D58" t="str">
-        <v>From **19 February 2025** to **24 December 2025**, **Caros** conducted a total of **255** live streams on **TikTok**, achieving **extraordinary outcomes** in the livestream field. Links to these achievements: {{%ACH%}}</v>
+        <v>From 19 February 2025 to 24 December 2025, Caros conducted a total of 255 live streams on TikTok, achieving extraordinary outcomes in the livestream field. Links to these achievements: {{%ACH%}}</v>
       </c>
       <c r="E58" t="str">
-        <v>从**2025年2月19日**至**12月24日**，**Caros**在TikTok上总共进行了**255**场直播，在直播间取得了**超凡的成就**。这些成就的链接在：{{%ACH%}}</v>
+        <v>从2025年2月19日至12月24日，Caros在TikTok上总共进行了255场直播，在直播间取得了超凡的成就。这些成就的链接在：{{%ACH%}}</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -1773,10 +1773,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D60" t="str">
-        <v>A great number of **master spirits** and **hybrid spirits** reached out to us as father and sons, letting us know that the **spirit world** surprisingly has **administrators and creators**. **Master spirits**has given us a lot of help. Caros has obtained the PRCASG super power to remotely control the attached spirits ghosts in North America, so that Caros can directly remotely control the m on the other side of the world in China.This kind of PRCASG super power is the basis for us to build ASRA</v>
+        <v>A great number of master spirits and hybrid spirits reached out to us as father and sons, letting us know that the spirit world surprisingly has administrators and creators. Master spirits gave us a great deal of help. Caros obtained the PRCASG superpower to remotely control attached spirits in North America, so that while in China he could remotely control spirits on the other side of the globe. This PRCASG superpower is the basis on which we built ASRA.</v>
       </c>
       <c r="E60" t="str">
-        <v>大量**高级控制灵**（master spirit）以及**混合控制灵**（hybrid spirit）与我们父子联系，让我们知道灵魂世界竟然有**管理者和造物主**。高级控制灵给我们很多帮助，Caros获得了远程控制北美附体鬼魂的PRCASG超能力，让Caros在中国就可以直接远程控制远在地球另一端北美的附体鬼魂。这种PRCASG超能力正是我们建设ASRA的基础</v>
+        <v>大量高级控制灵（master spirit）以及混合控制灵（hybrid spirit）与我们父子联系，让我们知道灵魂世界竟然有管理者和造物主。高级控制灵给我们很多帮助，Caros获得了远程控制北美附体鬼魂的PRCASG超能力，让Caros在中国就可以直接远程控制远在地球另一端北美的附体鬼魂。这种PRCASG超能力正是我们建设ASRA的基础</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -1819,10 +1819,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D62" t="str">
-        <v>**Most importantly**, we were told: every attached ghost on us during **Phase A** was **deliberately arranged** by **master spirits**. The killing of those attached ghosts was **permitted as research material**. All the **suffering, deception, and taunting storylines** were also part of their plan — to let us understand their **operating style and character disposition**.</v>
+        <v>Most importantly, we were told: every attached ghost on us during Phase A was deliberately arranged by master spirits. The killing of those attached ghosts was permitted as research material. All the suffering, deception, and taunting storylines were also part of their plan — to let us understand their operating style and character disposition.</v>
       </c>
       <c r="E62" t="str">
-        <v>**最重要的是**，我们被告知，A阶段在我们身上附体的鬼魂都是被**高级控制灵**（master spirit）**刻意安排**进来的。这些附体鬼魂被杀死是被**许可作为研究使用**的。所有的**病痛折磨**、**欺骗**、**戏弄性的故事**也是他们计划的一部分，让我们了解到了他们的**做事风格以及性格秉性**。</v>
+        <v>最重要的是，我们被告知，A阶段在我们身上附体的鬼魂都是被高级控制灵（master spirit）刻意安排进来的。这些附体鬼魂被杀死是被许可作为研究使用的。所有的病痛折磨、欺骗、戏弄性的故事也是他们计划的一部分，让我们了解到了他们的做事风格以及性格秉性。</v>
       </c>
       <c r="F62" t="str">
         <v/>
@@ -1865,10 +1865,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D64" t="str">
-        <v>This also let us fully understand: **master spirits** are **not** as **angel-like kind** as we imagined. The help provided earlier was **not** out of **kindness** but was work **assigned to them by the Universal Matrix of Meta Awareness**. Everyone can fully appreciate the **character attributes of the master spirit team** through the **Phase A stories**.</v>
+        <v>This also let us fully understand: master spirits are not as angel-like kind as we imagined. The help provided earlier was not out of kindness but was work assigned to them by the **Universal Matrix of Meta Awareness**. Everyone can fully appreciate the character attributes of the master spirit team through the Phase A stories.</v>
       </c>
       <c r="E64" t="str">
-        <v>这也让我们**完整**地了解到了**高级控制灵**（master spirit）并非像我们想象中的有**天使般的善良**，前面提供的帮助并非出于**善良**而是**万有元神母体**给他们**安排的工作**。大家可以通过**A阶段故事**充分体会master spirit团队的**性格属性**。</v>
+        <v>这也让我们完整地了解到了高级控制灵（master spirit）并非像我们想象中的有天使般的善良，前面提供的帮助并非出于善良而是**万有元神母体**给他们安排的工作。大家可以通过A阶段故事充分体会master spirit团队的性格属性。</v>
       </c>
       <c r="F64" t="str">
         <v/>
@@ -1911,10 +1911,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D66" t="str">
-        <v>During this period, **Spirit Medicine was formally established**. Part of the **Woos Spirit Medicine** and **Universal Matrix of Meta Awareness** video archive series were filmed.</v>
+        <v>During this period, Spirit Medicine was formally established. Part of the **Woos Spirit Medicine** and **Universal Matrix of Meta Awareness** video archive series were filmed.</v>
       </c>
       <c r="E66" t="str">
-        <v>在此期间，**正式创建**了**吴氏灵魂医学**。拍摄了**吴氏灵魂医学**和**万有元神母体**系列视频档案中的**一部分**视频。</v>
+        <v>在此期间，正式创建了**吴氏灵魂医学**。拍摄了**吴氏灵魂医学**和**万有元神母体**系列视频档案中的一部分视频。</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -2236,7 +2236,7 @@
         <v>PhaseB . Tiktok livestream &amp; the born of Spirit medicine</v>
       </c>
       <c r="E80" t="str">
-        <v>B阶段 · TikTok 直播与吴氏灵魂医学档案</v>
+        <v>B阶段 · TikTok 直播与**吴氏灵魂医学**档案</v>
       </c>
       <c r="F80" t="str">
         <v/>

--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -437,10 +437,10 @@
         <v>label</v>
       </c>
       <c r="D2" t="str">
-        <v>John Long Woo · Caros · Sam</v>
+        <v>John Long Woo · Caros Woo · Sam</v>
       </c>
       <c r="E2" t="str">
-        <v>John Long Woo· Caros · Sam</v>
+        <v>John Long Woo· Caros Woo · Sam</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -529,10 +529,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v>I, John LONG WOO, and my two sons Caros and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of spirit life.</v>
+        <v>I, John LONG WOO, and my two sons Caros Woo and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of spirit life.</v>
       </c>
       <c r="E6" t="str">
-        <v>我， John LONG WOO, 和我的两个儿子Caros和Sam，我们父子三人，与灵魂世界有太多传奇的故事。这些经历造就我们是灵魂世界首位开门者，并且是灵魂生命真相的首位探索者。</v>
+        <v>我， John LONG WOO, 和我的两个儿子Caros Woo和Sam，我们父子三人，与灵魂世界有太多传奇的故事。这些经历造就我们是灵魂世界首位开门者，并且是灵魂生命真相的首位探索者。</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -1681,10 +1681,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D56" t="str">
-        <v>In this phase, Caros communicated with a large number of attached ghosts in North America through TikTok live streams, completely confirming all the spirit world truths we obtained in Phase A. With the help of master spirits, Caros obtained the superpower to remotely control attached ghosts in North America. This superpower is the foundation upon which we built ASRA.</v>
+        <v>In this phase, Caros Woo communicated with a large number of attached ghosts in North America through TikTok live streams, completely confirming all the spirit world truths we obtained in Phase A. With the help of master spirits, Caros Woo obtained the superpower to remotely control attached ghosts in North America. This superpower is the foundation upon which we built ASRA.</v>
       </c>
       <c r="E56" t="str">
-        <v>在这个阶段，Caros通过TikTok直播间与北美的大量附体鬼魂进行了交流，完全证实了A阶段我们获得的所有灵魂世界真相。并且在高级控制灵的帮助下，Caros获得了远程控制北美附体鬼魂的超能力。这种超能力正是我们建设ASRA的基础。</v>
+        <v>在这个阶段，Caros Woo通过TikTok直播间与北美的大量附体鬼魂进行了交流，完全证实了A阶段我们获得的所有灵魂世界真相。并且在高级控制灵的帮助下，Caros Woo获得了远程控制北美附体鬼魂的超能力。这种超能力正是我们建设ASRA的基础。</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -1727,10 +1727,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D58" t="str">
-        <v>From 19 February 2025 to 24 December 2025, Caros conducted a total of 255 live streams on TikTok, achieving extraordinary outcomes in the livestream field. Links to these achievements: {{%ACH%}}</v>
+        <v>From 19 February 2025 to 24 December 2025, Caros Woo conducted a total of 255 live streams on TikTok, achieving extraordinary outcomes in the livestream field. Links to these achievements: {{%ACH%}}</v>
       </c>
       <c r="E58" t="str">
-        <v>从2025年2月19日至12月24日，Caros在TikTok上总共进行了255场直播，在直播间取得了超凡的成就。这些成就的链接在：{{%ACH%}}</v>
+        <v>从2025年2月19日至12月24日，Caros Woo在TikTok上总共进行了255场直播，在直播间取得了超凡的成就。这些成就的链接在：{{%ACH%}}</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -1773,10 +1773,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D60" t="str">
-        <v>A great number of master spirits and hybrid spirits reached out to us as father and sons, letting us know that the spirit world surprisingly has administrators and creators. Master spirits gave us a great deal of help. Caros obtained the PRCASG superpower to remotely control attached spirits in North America, so that while in China he could remotely control spirits on the other side of the globe. This PRCASG superpower is the basis on which we built ASRA.</v>
+        <v>A great number of master spirits and hybrid spirits reached out to us as father and sons, letting us know that the spirit world surprisingly has administrators and creators. Master spirits gave us a great deal of help. Caros Woo obtained the PRCASG superpower to remotely control attached spirits in North America, so that while in China he could remotely control spirits on the other side of the globe. This PRCASG superpower is the basis on which we built ASRA.</v>
       </c>
       <c r="E60" t="str">
-        <v>大量高级控制灵（master spirit）以及混合控制灵（hybrid spirit）与我们父子联系，让我们知道灵魂世界竟然有管理者和造物主。高级控制灵给我们很多帮助，Caros获得了远程控制北美附体鬼魂的PRCASG超能力，让Caros在中国就可以直接远程控制远在地球另一端北美的附体鬼魂。这种PRCASG超能力正是我们建设ASRA的基础</v>
+        <v>大量高级控制灵（master spirit）以及混合控制灵（hybrid spirit）与我们父子联系，让我们知道灵魂世界竟然有管理者和造物主。高级控制灵给我们很多帮助，Caros Woo获得了远程控制北美附体鬼魂的PRCASG超能力，让Caros Woo在中国就可以直接远程控制远在地球另一端北美的附体鬼魂。这种PRCASG超能力正是我们建设ASRA的基础</v>
       </c>
       <c r="F60" t="str">
         <v/>

--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -1680,10 +1680,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D56" t="str">
-        <v>In this phase, Caros Woo communicated with a large number of attached **spirits (ghosts)** in North America through TikTok live streams, completely confirming all the spirit world truths we obtained in Phase A. With the help of master spirits, Caros Woo obtained the superpower to remotely control attached **spirits (ghosts)** in North America. This superpower is the foundation upon which we built ASRA.</v>
+        <v xml:space="preserve">In this phase, Caros Woo communicated with a large number of attached **spirits (ghosts)** in North America through TikTok live streams, completely confirming all the spirit world truths we obtained in Phase A. </v>
       </c>
       <c r="E56" t="str">
-        <v>在这个阶段，Caros Woo通过TikTok直播间与北美的大量附体鬼魂进行了交流，完全证实了A阶段我们获得的所有灵魂世界真相。并且在高级控制灵的帮助下，Caros Woo获得了远程控制北美附体鬼魂的超能力。这种超能力正是我们建设ASRA的基础。</v>
+        <v>在这个阶段，Caros Woo通过TikTok直播间与北美的大量附体鬼魂进行了交流，完全证实了A阶段我们获得的所有灵魂世界真相。</v>
       </c>
       <c r="F56" t="str">
         <v/>
